--- a/models/userrole.xlsx
+++ b/models/userrole.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/rbac/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDFF82B-C7E4-C640-9303-097FB9FCDF19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5FF68B-C582-294D-9CEF-F5B62517809F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19840" yWindow="15460" windowWidth="27040" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5100" yWindow="7940" windowWidth="27040" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
     <sheet name="fields" sheetId="2" r:id="rId2"/>
     <sheet name="validation" sheetId="3" r:id="rId3"/>
-    <sheet name="codes" sheetId="6" r:id="rId4"/>
-    <sheet name="coding" sheetId="4" r:id="rId5"/>
-    <sheet name="help" sheetId="5" r:id="rId6"/>
+    <sheet name="data" sheetId="7" r:id="rId4"/>
+    <sheet name="codes" sheetId="6" r:id="rId5"/>
+    <sheet name="coding" sheetId="4" r:id="rId6"/>
+    <sheet name="help" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="87">
   <si>
     <t>name</t>
   </si>
@@ -285,6 +286,18 @@
   </si>
   <si>
     <t>(select id, concat(orgtypeid, '.', name) as name from role) as a</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>user-01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>role-01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ur-01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -911,6 +924,39 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B69F93D5-CF77-7347-8BFA-0ABB10953F43}">
+  <dimension ref="C1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="3:5">
+      <c r="C1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="3:5">
+      <c r="C2" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034F9041-5299-834D-9251-2648BE5D48B1}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
@@ -969,7 +1015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
@@ -1097,7 +1143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
